--- a/saucedemo/bugReport.xlsx
+++ b/saucedemo/bugReport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MOHAMED\job\Software Testing [ QA ]\Projects\saucedemo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103733CD-176D-4321-8D29-CA2FD3146551}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB9AFBB-5075-4FDB-9B0D-2D33F297635C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{67B74E7F-BD0F-4CD3-A78B-2C371E4B02E6}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="93">
   <si>
     <t>Category</t>
   </si>
@@ -329,6 +329,44 @@
   </si>
   <si>
     <t>The Filter does not working</t>
+  </si>
+  <si>
+    <t>LastName field</t>
+  </si>
+  <si>
+    <t>Last Name field does not accept text input</t>
+  </si>
+  <si>
+    <t>1-Connected WIFI
+2-Browser "chrome 126" is opened
+3-URL "https://www.saucedemo.com/" is navigated
+4-Log in using the problem_user account
+5- open the cart page 
+6-Click Click the Last Name field.</t>
+  </si>
+  <si>
+    <t>The Last Name field accepts text input</t>
+  </si>
+  <si>
+    <t>The Last Name field does not accept text input.</t>
+  </si>
+  <si>
+    <t>Bug_#001.mp4</t>
+  </si>
+  <si>
+    <t>Bug_#002.mp4</t>
+  </si>
+  <si>
+    <t>Bug_#003.mp4</t>
+  </si>
+  <si>
+    <t>Bug_#004.mp4</t>
+  </si>
+  <si>
+    <t>Bug_#005.mp4</t>
+  </si>
+  <si>
+    <t>Bug_#006.mp4</t>
   </si>
 </sst>
 </file>
@@ -457,7 +495,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -528,6 +566,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -981,7 +1022,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{786740B8-3279-4CBF-917D-83443D77D26C}">
-  <dimension ref="B2:H20"/>
+  <dimension ref="B2:I20"/>
   <sheetFormatPr defaultColWidth="38.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.5546875" customWidth="1"/>
@@ -993,7 +1034,7 @@
     <col min="8" max="8" width="42.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="14" t="s">
         <v>0</v>
       </c>
@@ -1015,8 +1056,11 @@
       <c r="H2" s="5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I2" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B3" s="19" t="s">
         <v>3</v>
       </c>
@@ -1038,8 +1082,11 @@
       <c r="H3" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="4" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I3" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B4" s="20"/>
       <c r="C4" s="16" t="s">
         <v>6</v>
@@ -1059,8 +1106,11 @@
       <c r="H4" s="1" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="5" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I4" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="20"/>
       <c r="C5" s="16" t="s">
         <v>7</v>
@@ -1080,8 +1130,11 @@
       <c r="H5" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="6" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I5" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="21"/>
       <c r="C6" s="16" t="s">
         <v>8</v>
@@ -1101,8 +1154,11 @@
       <c r="H6" s="2">
         <v>46089</v>
       </c>
-    </row>
-    <row r="7" spans="2:8" ht="58.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I6" s="2">
+        <v>46089</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="58.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="19" t="s">
         <v>9</v>
       </c>
@@ -1124,8 +1180,11 @@
       <c r="H7" s="6" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="8" spans="2:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I7" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="20"/>
       <c r="C8" s="16" t="s">
         <v>11</v>
@@ -1145,19 +1204,35 @@
       <c r="H8" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="9" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I8" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B9" s="21"/>
       <c r="C9" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-    </row>
-    <row r="10" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="D9" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B10" s="19" t="s">
         <v>13</v>
       </c>
@@ -1179,8 +1254,11 @@
       <c r="H10" s="1" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="11" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I10" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B11" s="20"/>
       <c r="C11" s="16" t="s">
         <v>15</v>
@@ -1200,8 +1278,11 @@
       <c r="H11" s="1" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="12" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I11" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B12" s="21"/>
       <c r="C12" s="16" t="s">
         <v>16</v>
@@ -1221,8 +1302,11 @@
       <c r="H12" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="13" spans="2:8" ht="159.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I12" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" ht="175.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="19" t="s">
         <v>18</v>
       </c>
@@ -1244,8 +1328,11 @@
       <c r="H13" s="7" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="14" spans="2:8" ht="66" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I13" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" ht="66" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="20"/>
       <c r="C14" s="16" t="s">
         <v>20</v>
@@ -1265,8 +1352,11 @@
       <c r="H14" s="18" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="15" spans="2:8" ht="75.599999999999994" x14ac:dyDescent="0.3">
+      <c r="I14" s="25" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" ht="75.599999999999994" x14ac:dyDescent="0.3">
       <c r="B15" s="20"/>
       <c r="C15" s="16" t="s">
         <v>21</v>
@@ -1286,8 +1376,11 @@
       <c r="H15" s="10" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="16" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I15" s="10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B16" s="21"/>
       <c r="C16" s="16" t="s">
         <v>22</v>
@@ -1297,8 +1390,9 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
-    </row>
-    <row r="17" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B17" s="19" t="s">
         <v>23</v>
       </c>
@@ -1320,8 +1414,11 @@
       <c r="H17" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I17" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B18" s="20"/>
       <c r="C18" s="16" t="s">
         <v>25</v>
@@ -1331,8 +1428,9 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
-    </row>
-    <row r="19" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B19" s="21"/>
       <c r="C19" s="16" t="s">
         <v>26</v>
@@ -1352,8 +1450,11 @@
       <c r="H19" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="20" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I19" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B20" s="14" t="s">
         <v>27</v>
       </c>
@@ -1365,6 +1466,7 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1380,6 +1482,7 @@
     <hyperlink ref="F8" r:id="rId3" xr:uid="{3900DF3F-C0F7-427B-8683-D90EFAD9A8A1}"/>
     <hyperlink ref="G8" r:id="rId4" xr:uid="{2BCF9710-2952-4941-B6F4-82B95883CAE2}"/>
     <hyperlink ref="H8" r:id="rId5" xr:uid="{26677412-FF41-41A7-BD87-E0416EB687F1}"/>
+    <hyperlink ref="I8" r:id="rId6" xr:uid="{410DC64E-29C5-4181-999B-58187C2F78A3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/saucedemo/bugReport.xlsx
+++ b/saucedemo/bugReport.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MOHAMED\job\Software Testing [ QA ]\Projects\saucedemo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB9AFBB-5075-4FDB-9B0D-2D33F297635C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5F43574-5B4F-48FD-A696-4EA00D1BD6ED}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{67B74E7F-BD0F-4CD3-A78B-2C371E4B02E6}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" activeTab="1" xr2:uid="{67B74E7F-BD0F-4CD3-A78B-2C371E4B02E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="94">
   <si>
     <t>Category</t>
   </si>
@@ -367,6 +367,9 @@
   </si>
   <si>
     <t>Bug_#006.mp4</t>
+  </si>
+  <si>
+    <t>#009</t>
   </si>
 </sst>
 </file>
@@ -549,6 +552,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -566,9 +572,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1061,7 +1064,7 @@
       </c>
     </row>
     <row r="3" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="16" t="s">
@@ -1087,7 +1090,7 @@
       </c>
     </row>
     <row r="4" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B4" s="20"/>
+      <c r="B4" s="21"/>
       <c r="C4" s="16" t="s">
         <v>6</v>
       </c>
@@ -1111,7 +1114,7 @@
       </c>
     </row>
     <row r="5" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B5" s="20"/>
+      <c r="B5" s="21"/>
       <c r="C5" s="16" t="s">
         <v>7</v>
       </c>
@@ -1135,7 +1138,7 @@
       </c>
     </row>
     <row r="6" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="21"/>
+      <c r="B6" s="22"/>
       <c r="C6" s="16" t="s">
         <v>8</v>
       </c>
@@ -1159,7 +1162,7 @@
       </c>
     </row>
     <row r="7" spans="2:9" ht="58.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="20" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="16" t="s">
@@ -1185,7 +1188,7 @@
       </c>
     </row>
     <row r="8" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="20"/>
+      <c r="B8" s="21"/>
       <c r="C8" s="16" t="s">
         <v>11</v>
       </c>
@@ -1209,7 +1212,7 @@
       </c>
     </row>
     <row r="9" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="21"/>
+      <c r="B9" s="22"/>
       <c r="C9" s="16" t="s">
         <v>12</v>
       </c>
@@ -1233,7 +1236,7 @@
       </c>
     </row>
     <row r="10" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="20" t="s">
         <v>13</v>
       </c>
       <c r="C10" s="16" t="s">
@@ -1259,7 +1262,7 @@
       </c>
     </row>
     <row r="11" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B11" s="20"/>
+      <c r="B11" s="21"/>
       <c r="C11" s="16" t="s">
         <v>15</v>
       </c>
@@ -1283,7 +1286,7 @@
       </c>
     </row>
     <row r="12" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B12" s="21"/>
+      <c r="B12" s="22"/>
       <c r="C12" s="16" t="s">
         <v>16</v>
       </c>
@@ -1307,7 +1310,7 @@
       </c>
     </row>
     <row r="13" spans="2:9" ht="175.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="20" t="s">
         <v>18</v>
       </c>
       <c r="C13" s="16" t="s">
@@ -1333,7 +1336,7 @@
       </c>
     </row>
     <row r="14" spans="2:9" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="20"/>
+      <c r="B14" s="21"/>
       <c r="C14" s="16" t="s">
         <v>20</v>
       </c>
@@ -1352,12 +1355,12 @@
       <c r="H14" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="I14" s="25" t="s">
+      <c r="I14" s="19" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="75.599999999999994" x14ac:dyDescent="0.3">
-      <c r="B15" s="20"/>
+      <c r="B15" s="21"/>
       <c r="C15" s="16" t="s">
         <v>21</v>
       </c>
@@ -1381,7 +1384,7 @@
       </c>
     </row>
     <row r="16" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B16" s="21"/>
+      <c r="B16" s="22"/>
       <c r="C16" s="16" t="s">
         <v>22</v>
       </c>
@@ -1393,7 +1396,7 @@
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="20" t="s">
         <v>23</v>
       </c>
       <c r="C17" s="16" t="s">
@@ -1419,7 +1422,7 @@
       </c>
     </row>
     <row r="18" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B18" s="20"/>
+      <c r="B18" s="21"/>
       <c r="C18" s="16" t="s">
         <v>25</v>
       </c>
@@ -1431,7 +1434,7 @@
       <c r="I18" s="1"/>
     </row>
     <row r="19" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B19" s="21"/>
+      <c r="B19" s="22"/>
       <c r="C19" s="16" t="s">
         <v>26</v>
       </c>
@@ -1520,24 +1523,24 @@
       </c>
     </row>
     <row r="3" spans="4:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="23" t="s">
         <v>3</v>
       </c>
       <c r="E3" s="16" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="4:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D4" s="23"/>
+      <c r="D4" s="24"/>
       <c r="E4" s="16" t="s">
         <v>6</v>
       </c>
@@ -1552,7 +1555,7 @@
       </c>
     </row>
     <row r="5" spans="4:8" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D5" s="23"/>
+      <c r="D5" s="24"/>
       <c r="E5" s="17" t="s">
         <v>7</v>
       </c>
@@ -1567,7 +1570,7 @@
       </c>
     </row>
     <row r="6" spans="4:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D6" s="24"/>
+      <c r="D6" s="25"/>
       <c r="E6" s="16" t="s">
         <v>8</v>
       </c>
@@ -1582,7 +1585,7 @@
       </c>
     </row>
     <row r="7" spans="4:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="23" t="s">
         <v>9</v>
       </c>
       <c r="E7" s="16" t="s">
@@ -1599,7 +1602,7 @@
       </c>
     </row>
     <row r="8" spans="4:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D8" s="23"/>
+      <c r="D8" s="24"/>
       <c r="E8" s="16" t="s">
         <v>11</v>
       </c>
@@ -1614,7 +1617,7 @@
       </c>
     </row>
     <row r="9" spans="4:8" ht="265.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D9" s="24"/>
+      <c r="D9" s="25"/>
       <c r="E9" s="16" t="s">
         <v>12</v>
       </c>
@@ -1623,7 +1626,7 @@
       <c r="H9" s="1"/>
     </row>
     <row r="10" spans="4:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="23" t="s">
         <v>13</v>
       </c>
       <c r="E10" s="16" t="s">
@@ -1640,7 +1643,7 @@
       </c>
     </row>
     <row r="11" spans="4:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D11" s="23"/>
+      <c r="D11" s="24"/>
       <c r="E11" s="16" t="s">
         <v>15</v>
       </c>
@@ -1655,7 +1658,7 @@
       </c>
     </row>
     <row r="12" spans="4:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D12" s="24"/>
+      <c r="D12" s="25"/>
       <c r="E12" s="16" t="s">
         <v>16</v>
       </c>
@@ -1670,7 +1673,7 @@
       </c>
     </row>
     <row r="13" spans="4:8" ht="105" x14ac:dyDescent="0.3">
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="23" t="s">
         <v>18</v>
       </c>
       <c r="E13" s="16" t="s">
@@ -1687,7 +1690,7 @@
       </c>
     </row>
     <row r="14" spans="4:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D14" s="23"/>
+      <c r="D14" s="24"/>
       <c r="E14" s="16" t="s">
         <v>20</v>
       </c>
@@ -1702,7 +1705,7 @@
       </c>
     </row>
     <row r="15" spans="4:8" ht="30.6" x14ac:dyDescent="0.3">
-      <c r="D15" s="23"/>
+      <c r="D15" s="24"/>
       <c r="E15" s="16" t="s">
         <v>21</v>
       </c>
@@ -1717,7 +1720,7 @@
       </c>
     </row>
     <row r="16" spans="4:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D16" s="24"/>
+      <c r="D16" s="25"/>
       <c r="E16" s="16" t="s">
         <v>22</v>
       </c>
@@ -1726,7 +1729,7 @@
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="4:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="23" t="s">
         <v>23</v>
       </c>
       <c r="E17" s="16" t="s">
@@ -1743,7 +1746,7 @@
       </c>
     </row>
     <row r="18" spans="4:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D18" s="23"/>
+      <c r="D18" s="24"/>
       <c r="E18" s="16" t="s">
         <v>25</v>
       </c>
@@ -1752,7 +1755,7 @@
       <c r="H18" s="1"/>
     </row>
     <row r="19" spans="4:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D19" s="24"/>
+      <c r="D19" s="25"/>
       <c r="E19" s="16" t="s">
         <v>26</v>
       </c>
